--- a/dist/EQUIL_Light_v0_2.xlsx
+++ b/dist/EQUIL_Light_v0_2.xlsx
@@ -2290,7 +2290,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="I5:I16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valoare neacceptată" error="Valoare în afara listei permise. Alege din listă sau completează lista de valori." type="list">
-      <formula1>='02_SETARI'!$F$6:$F$9</formula1>
+      <formula1>'02_SETARI'!$F$6:$F$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3224,7 +3224,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valoare neacceptată" error="Valoare în afara listei permise. Alege din listă sau completează lista de valori." type="list">
-      <formula1>='02_SETARI'!$H$6:$H$8</formula1>
+      <formula1>'02_SETARI'!$H$6:$H$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15937,7 +15937,7 @@
   <autoFilter ref="A4:J604"/>
   <dataValidations count="1">
     <dataValidation sqref="B5:B604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valoare neacceptată" error="Valoare în afara listei permise. Alege din listă sau completează lista de valori." type="list">
-      <formula1>='11_CLIENTI'!$A$5:$A$124</formula1>
+      <formula1>'11_CLIENTI'!$A$5:$A$124</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17111,7 +17111,7 @@
   <autoFilter ref="A4:G124"/>
   <dataValidations count="1">
     <dataValidation sqref="B5:B124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valoare neacceptată" error="Valoare în afara listei permise. Alege din listă sau completează lista de valori." type="list">
-      <formula1>='02_SETARI'!$E$6:$E$9</formula1>
+      <formula1>'02_SETARI'!$E$6:$E$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17595,19 +17595,19 @@
   </sheetData>
   <autoFilter ref="A4:M14"/>
   <conditionalFormatting sqref="M5:M14">
-    <cfRule type="cellIs" priority="1" operator="containsText" dxfId="0">
-      <formula>NOT(ISERROR(SEARCH("E mai bine văzut",M5)))</formula>
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>ISNUMBER(SEARCH("E mai bine văzut",M5))</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="containsText" dxfId="1">
-      <formula>NOT(ISERROR(SEARCH("Suntem mai bine văzuți",M5)))</formula>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>ISNUMBER(SEARCH("Suntem mai bine",M5))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valoare neacceptată" error="Valoare în afara listei permise. Alege din listă sau completează lista de valori." type="list">
-      <formula1>='12_CONCURENTA'!$Y$2:$Y$6</formula1>
+      <formula1>'12_CONCURENTA'!$Y$2:$Y$6</formula1>
     </dataValidation>
     <dataValidation sqref="I5:I14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valoare neacceptată" error="Valoare în afara listei permise. Alege din listă sau completează lista de valori." type="list">
-      <formula1>='12_CONCURENTA'!$Z$2:$Z$7</formula1>
+      <formula1>'12_CONCURENTA'!$Z$2:$Z$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18397,7 +18397,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="A6:A11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valoare neacceptată" error="Valoare în afara listei permise. Alege din listă sau completează lista de valori." type="list">
-      <formula1>='13_CE_CRED_OAMENII'!$Z$2:$Z$9</formula1>
+      <formula1>'13_CE_CRED_OAMENII'!$Z$2:$Z$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18834,7 +18834,7 @@
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="59">
-        <f>IF(AND(MAX(0,COUNTA('12_CONCURENTA'!$A$5:$A$14)-1)=0,SUMPRODUCT(('13_CE_CRED_OAMENII'!$D$6:$D$11&lt;&gt;"")*'13_CE_CRED_OAMENII'!$E$6:$E$11)=0),"Nu ai completat încă nimic despre concurență și reputație (foile 12 și 13). E cel mai ieftin context din tot fișierul: o oră pe internet, fără să întrebi pe nimeni.","Urmărim "&amp;FIXED(MAX(0,COUNTA('12_CONCURENTA'!$A$5:$A$14)-1),0)&amp;" concurenți. "&amp;IF('12_CONCURENTA'!$F$5="","Firma nu are încă notă publică — verifică dacă are fișă Google Business. Un client nou o caută acolo înainte să sune.","Nota publică e "&amp;FIXED('12_CONCURENTA'!$F$5,1)&amp;" din 5"&amp;IF(IFERROR(AVERAGE('12_CONCURENTA'!$F$6:$F$14),"")="","."," , față de "&amp;FIXED(IFERROR(AVERAGE('12_CONCURENTA'!$F$6:$F$14),""),1)&amp;" media concurenților"&amp;IF('12_CONCURENTA'!$F$5&gt;IFERROR(AVERAGE('12_CONCURENTA'!$F$6:$F$14),"")+0.2," — stăm mai bine decât ei.",IF('12_CONCURENTA'!$F$5&lt;IFERROR(AVERAGE('12_CONCURENTA'!$F$6:$F$14),"")-0.2," — stăm mai slab; asta se rezolvă înainte de a crește volumul."," — la fel ca ei."))))&amp;IF(SUMPRODUCT(('11_CLIENTI'!$A$5:$A$124&lt;&gt;"")*('11_CLIENTI'!$D$5:$D$124&lt;&gt;""))=0," NPS nu e măsurat încă: scorul de percepție din foaia 13 ține locul, dar nu îl înlocuiește.",""))</f>
+        <f>IF(AND(MAX(0,COUNTA('12_CONCURENTA'!$A$5:$A$14)-1)=0,SUMPRODUCT(('13_CE_CRED_OAMENII'!$D$6:$D$11&lt;&gt;"")*'13_CE_CRED_OAMENII'!$E$6:$E$11)=0),"Nu ai completat încă nimic despre concurență și reputație (foile 12 și 13). E cel mai ieftin context din tot fișierul: o oră pe internet, fără să întrebi pe nimeni.","Urmărim "&amp;FIXED(MAX(0,COUNTA('12_CONCURENTA'!$A$5:$A$14)-1),0)&amp;" concurenți. "&amp;IF('12_CONCURENTA'!$F$5="","Firma nu are încă notă publică — verifică dacă are fișă Google Business. Un client nou o caută acolo înainte să sune.","Nota publică e "&amp;FIXED('12_CONCURENTA'!$F$5,1)&amp;" din 5"&amp;IF(IFERROR(AVERAGE('12_CONCURENTA'!$F$6:$F$14),"")="",".",", față de "&amp;FIXED(IFERROR(AVERAGE('12_CONCURENTA'!$F$6:$F$14),""),1)&amp;" media concurenților"&amp;IF('12_CONCURENTA'!$F$5&gt;IFERROR(AVERAGE('12_CONCURENTA'!$F$6:$F$14),"")+0.2," — stăm mai bine decât ei.",IF('12_CONCURENTA'!$F$5&lt;IFERROR(AVERAGE('12_CONCURENTA'!$F$6:$F$14),"")-0.2," — stăm mai slab; asta se rezolvă înainte de a crește volumul."," — la fel ca ei."))))&amp;IF(SUMPRODUCT(('11_CLIENTI'!$A$5:$A$124&lt;&gt;"")*('11_CLIENTI'!$D$5:$D$124&lt;&gt;""))=0," NPS nu e măsurat încă: scorul de percepție din foaia 13 ține locul, dar nu îl înlocuiește.",""))</f>
         <v/>
       </c>
     </row>

--- a/dist/EQUIL_Light_v0_2.xlsx
+++ b/dist/EQUIL_Light_v0_2.xlsx
@@ -2418,7 +2418,7 @@
         <v>0.9</v>
       </c>
       <c r="F5" s="21">
-        <f>IF($D5="","",N($D5)*N($E5))</f>
+        <f>IF(OR($D5="",$E5=""),"",$D5*$E5)</f>
         <v/>
       </c>
       <c r="G5" s="37">
@@ -2450,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="21">
-        <f>IF($D6="","",N($D6)*N($E6))</f>
+        <f>IF(OR($D6="",$E6=""),"",$D6*$E6)</f>
         <v/>
       </c>
       <c r="G6" s="37">
@@ -2482,7 +2482,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="21">
-        <f>IF($D7="","",N($D7)*N($E7))</f>
+        <f>IF(OR($D7="",$E7=""),"",$D7*$E7)</f>
         <v/>
       </c>
       <c r="G7" s="37">
@@ -2504,7 +2504,7 @@
       <c r="D8" s="36" t="n"/>
       <c r="E8" s="77" t="n"/>
       <c r="F8" s="21">
-        <f>IF($D8="","",N($D8)*N($E8))</f>
+        <f>IF(OR($D8="",$E8=""),"",$D8*$E8)</f>
         <v/>
       </c>
       <c r="G8" s="37">
@@ -2522,7 +2522,7 @@
       <c r="D9" s="36" t="n"/>
       <c r="E9" s="77" t="n"/>
       <c r="F9" s="21">
-        <f>IF($D9="","",N($D9)*N($E9))</f>
+        <f>IF(OR($D9="",$E9=""),"",$D9*$E9)</f>
         <v/>
       </c>
       <c r="G9" s="37">
@@ -2540,7 +2540,7 @@
       <c r="D10" s="36" t="n"/>
       <c r="E10" s="77" t="n"/>
       <c r="F10" s="21">
-        <f>IF($D10="","",N($D10)*N($E10))</f>
+        <f>IF(OR($D10="",$E10=""),"",$D10*$E10)</f>
         <v/>
       </c>
       <c r="G10" s="37">
@@ -2558,7 +2558,7 @@
       <c r="D11" s="36" t="n"/>
       <c r="E11" s="77" t="n"/>
       <c r="F11" s="21">
-        <f>IF($D11="","",N($D11)*N($E11))</f>
+        <f>IF(OR($D11="",$E11=""),"",$D11*$E11)</f>
         <v/>
       </c>
       <c r="G11" s="37">
@@ -2576,7 +2576,7 @@
       <c r="D12" s="36" t="n"/>
       <c r="E12" s="77" t="n"/>
       <c r="F12" s="21">
-        <f>IF($D12="","",N($D12)*N($E12))</f>
+        <f>IF(OR($D12="",$E12=""),"",$D12*$E12)</f>
         <v/>
       </c>
       <c r="G12" s="37">
@@ -2594,7 +2594,7 @@
       <c r="D13" s="36" t="n"/>
       <c r="E13" s="77" t="n"/>
       <c r="F13" s="21">
-        <f>IF($D13="","",N($D13)*N($E13))</f>
+        <f>IF(OR($D13="",$E13=""),"",$D13*$E13)</f>
         <v/>
       </c>
       <c r="G13" s="37">
@@ -2612,7 +2612,7 @@
       <c r="D14" s="36" t="n"/>
       <c r="E14" s="77" t="n"/>
       <c r="F14" s="21">
-        <f>IF($D14="","",N($D14)*N($E14))</f>
+        <f>IF(OR($D14="",$E14=""),"",$D14*$E14)</f>
         <v/>
       </c>
       <c r="G14" s="37">
@@ -2630,7 +2630,7 @@
       <c r="D15" s="36" t="n"/>
       <c r="E15" s="77" t="n"/>
       <c r="F15" s="21">
-        <f>IF($D15="","",N($D15)*N($E15))</f>
+        <f>IF(OR($D15="",$E15=""),"",$D15*$E15)</f>
         <v/>
       </c>
       <c r="G15" s="37">
@@ -2648,7 +2648,7 @@
       <c r="D16" s="36" t="n"/>
       <c r="E16" s="77" t="n"/>
       <c r="F16" s="21">
-        <f>IF($D16="","",N($D16)*N($E16))</f>
+        <f>IF(OR($D16="",$E16=""),"",$D16*$E16)</f>
         <v/>
       </c>
       <c r="G16" s="37">
@@ -19650,7 +19650,7 @@
         <v/>
       </c>
       <c r="I5" s="76">
-        <f>IF($A5="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A5)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A5)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A5="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A5)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A5)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J5" s="74">
@@ -19712,7 +19712,7 @@
         <v/>
       </c>
       <c r="I6" s="76">
-        <f>IF($A6="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A6)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A6)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A6="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A6)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A6)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J6" s="74">
@@ -19774,7 +19774,7 @@
         <v/>
       </c>
       <c r="I7" s="76">
-        <f>IF($A7="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A7)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A7)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A7="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A7)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A7)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J7" s="74">
@@ -19836,7 +19836,7 @@
         <v/>
       </c>
       <c r="I8" s="76">
-        <f>IF($A8="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A8)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A8)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A8="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A8)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A8)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J8" s="74">
@@ -19898,7 +19898,7 @@
         <v/>
       </c>
       <c r="I9" s="76">
-        <f>IF($A9="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A9)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A9)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A9="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A9)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A9)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J9" s="74">
@@ -19960,7 +19960,7 @@
         <v/>
       </c>
       <c r="I10" s="76">
-        <f>IF($A10="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A10)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A10)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A10="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A10)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A10)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J10" s="74">
@@ -20022,7 +20022,7 @@
         <v/>
       </c>
       <c r="I11" s="76">
-        <f>IF($A11="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A11)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A11)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A11="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A11)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A11)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J11" s="74">
@@ -20084,7 +20084,7 @@
         <v/>
       </c>
       <c r="I12" s="76">
-        <f>IF($A12="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A12)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A12)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A12="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A12)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A12)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J12" s="74">
@@ -20146,7 +20146,7 @@
         <v/>
       </c>
       <c r="I13" s="76">
-        <f>IF($A13="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A13)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A13)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A13="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A13)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A13)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J13" s="74">
@@ -20208,7 +20208,7 @@
         <v/>
       </c>
       <c r="I14" s="76">
-        <f>IF($A14="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A14)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A14)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A14="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A14)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A14)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J14" s="74">
@@ -20270,7 +20270,7 @@
         <v/>
       </c>
       <c r="I15" s="76">
-        <f>IF($A15="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A15)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A15)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A15="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A15)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A15)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J15" s="74">
@@ -20332,7 +20332,7 @@
         <v/>
       </c>
       <c r="I16" s="76">
-        <f>IF($A16="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A16)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A16)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A16="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A16)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A16)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J16" s="74">
@@ -20394,7 +20394,7 @@
         <v/>
       </c>
       <c r="I17" s="76">
-        <f>IF($A17="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A17)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A17)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A17="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A17)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A17)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J17" s="74">
@@ -20456,7 +20456,7 @@
         <v/>
       </c>
       <c r="I18" s="76">
-        <f>IF($A18="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A18)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A18)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A18="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A18)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A18)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J18" s="74">
@@ -20518,7 +20518,7 @@
         <v/>
       </c>
       <c r="I19" s="76">
-        <f>IF($A19="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A19)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A19)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A19="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A19)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A19)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J19" s="74">
@@ -20580,7 +20580,7 @@
         <v/>
       </c>
       <c r="I20" s="76">
-        <f>IF($A20="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A20)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A20)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A20="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A20)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A20)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J20" s="74">
@@ -20642,7 +20642,7 @@
         <v/>
       </c>
       <c r="I21" s="76">
-        <f>IF($A21="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A21)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A21)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A21="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A21)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A21)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J21" s="74">
@@ -20704,7 +20704,7 @@
         <v/>
       </c>
       <c r="I22" s="76">
-        <f>IF($A22="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A22)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A22)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A22="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A22)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A22)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J22" s="74">
@@ -20766,7 +20766,7 @@
         <v/>
       </c>
       <c r="I23" s="76">
-        <f>IF($A23="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A23)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A23)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A23="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A23)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A23)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J23" s="74">
@@ -20828,7 +20828,7 @@
         <v/>
       </c>
       <c r="I24" s="76">
-        <f>IF($A24="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A24)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A24)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A24="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A24)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A24)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J24" s="74">
@@ -20890,7 +20890,7 @@
         <v/>
       </c>
       <c r="I25" s="76">
-        <f>IF($A25="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A25)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A25)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A25="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A25)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A25)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J25" s="74">
@@ -20952,7 +20952,7 @@
         <v/>
       </c>
       <c r="I26" s="76">
-        <f>IF($A26="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A26)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A26)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A26="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A26)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A26)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J26" s="74">
@@ -21014,7 +21014,7 @@
         <v/>
       </c>
       <c r="I27" s="76">
-        <f>IF($A27="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A27)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A27)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A27="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A27)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A27)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J27" s="74">
@@ -21076,7 +21076,7 @@
         <v/>
       </c>
       <c r="I28" s="76">
-        <f>IF($A28="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A28)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A28)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A28="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A28)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A28)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J28" s="74">
@@ -21138,7 +21138,7 @@
         <v/>
       </c>
       <c r="I29" s="76">
-        <f>IF($A29="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A29)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A29)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A29="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A29)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A29)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J29" s="74">
@@ -21200,7 +21200,7 @@
         <v/>
       </c>
       <c r="I30" s="76">
-        <f>IF($A30="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A30)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A30)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A30="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A30)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A30)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J30" s="74">
@@ -21262,7 +21262,7 @@
         <v/>
       </c>
       <c r="I31" s="76">
-        <f>IF($A31="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A31)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A31)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A31="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A31)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A31)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J31" s="74">
@@ -21324,7 +21324,7 @@
         <v/>
       </c>
       <c r="I32" s="76">
-        <f>IF($A32="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A32)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A32)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A32="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A32)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A32)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J32" s="74">
@@ -21386,7 +21386,7 @@
         <v/>
       </c>
       <c r="I33" s="76">
-        <f>IF($A33="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A33)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A33)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A33="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A33)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A33)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J33" s="74">
@@ -21448,7 +21448,7 @@
         <v/>
       </c>
       <c r="I34" s="76">
-        <f>IF($A34="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A34)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A34)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A34="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A34)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A34)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J34" s="74">
@@ -21510,7 +21510,7 @@
         <v/>
       </c>
       <c r="I35" s="76">
-        <f>IF($A35="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A35)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A35)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A35="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A35)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A35)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J35" s="74">
@@ -21572,7 +21572,7 @@
         <v/>
       </c>
       <c r="I36" s="76">
-        <f>IF($A36="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A36)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A36)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A36="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A36)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A36)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J36" s="74">
@@ -21634,7 +21634,7 @@
         <v/>
       </c>
       <c r="I37" s="76">
-        <f>IF($A37="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A37)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A37)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A37="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A37)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A37)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J37" s="74">
@@ -21696,7 +21696,7 @@
         <v/>
       </c>
       <c r="I38" s="76">
-        <f>IF($A38="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A38)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A38)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A38="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A38)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A38)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J38" s="74">
@@ -21758,7 +21758,7 @@
         <v/>
       </c>
       <c r="I39" s="76">
-        <f>IF($A39="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A39)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A39)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A39="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A39)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A39)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J39" s="74">
@@ -21820,7 +21820,7 @@
         <v/>
       </c>
       <c r="I40" s="76">
-        <f>IF($A40="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A40)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A40)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A40="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A40)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A40)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J40" s="74">
@@ -21882,7 +21882,7 @@
         <v/>
       </c>
       <c r="I41" s="76">
-        <f>IF($A41="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A41)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A41)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A41="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A41)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A41)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J41" s="74">
@@ -21944,7 +21944,7 @@
         <v/>
       </c>
       <c r="I42" s="76">
-        <f>IF($A42="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A42)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A42)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A42="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A42)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A42)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J42" s="74">
@@ -22006,7 +22006,7 @@
         <v/>
       </c>
       <c r="I43" s="76">
-        <f>IF($A43="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A43)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A43)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A43="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A43)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A43)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J43" s="74">
@@ -22068,7 +22068,7 @@
         <v/>
       </c>
       <c r="I44" s="76">
-        <f>IF($A44="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A44)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A44)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A44="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A44)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A44)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J44" s="74">
@@ -22130,7 +22130,7 @@
         <v/>
       </c>
       <c r="I45" s="76">
-        <f>IF($A45="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A45)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A45)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A45="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A45)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A45)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J45" s="74">
@@ -22192,7 +22192,7 @@
         <v/>
       </c>
       <c r="I46" s="76">
-        <f>IF($A46="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A46)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A46)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A46="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A46)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A46)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J46" s="74">
@@ -22254,7 +22254,7 @@
         <v/>
       </c>
       <c r="I47" s="76">
-        <f>IF($A47="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A47)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A47)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A47="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A47)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A47)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J47" s="74">
@@ -22316,7 +22316,7 @@
         <v/>
       </c>
       <c r="I48" s="76">
-        <f>IF($A48="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A48)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A48)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A48="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A48)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A48)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J48" s="74">
@@ -22378,7 +22378,7 @@
         <v/>
       </c>
       <c r="I49" s="76">
-        <f>IF($A49="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A49)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A49)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A49="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A49)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A49)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J49" s="74">
@@ -22440,7 +22440,7 @@
         <v/>
       </c>
       <c r="I50" s="76">
-        <f>IF($A50="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A50)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A50)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A50="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A50)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A50)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J50" s="74">
@@ -22502,7 +22502,7 @@
         <v/>
       </c>
       <c r="I51" s="76">
-        <f>IF($A51="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A51)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A51)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A51="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A51)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A51)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J51" s="74">
@@ -22564,7 +22564,7 @@
         <v/>
       </c>
       <c r="I52" s="76">
-        <f>IF($A52="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A52)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A52)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A52="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A52)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A52)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J52" s="74">
@@ -22626,7 +22626,7 @@
         <v/>
       </c>
       <c r="I53" s="76">
-        <f>IF($A53="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A53)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A53)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A53="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A53)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A53)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J53" s="74">
@@ -22688,7 +22688,7 @@
         <v/>
       </c>
       <c r="I54" s="76">
-        <f>IF($A54="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A54)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A54)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A54="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A54)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A54)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J54" s="74">
@@ -22750,7 +22750,7 @@
         <v/>
       </c>
       <c r="I55" s="76">
-        <f>IF($A55="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A55)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A55)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A55="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A55)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A55)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J55" s="74">
@@ -22812,7 +22812,7 @@
         <v/>
       </c>
       <c r="I56" s="76">
-        <f>IF($A56="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A56)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A56)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A56="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A56)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A56)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J56" s="74">
@@ -22874,7 +22874,7 @@
         <v/>
       </c>
       <c r="I57" s="76">
-        <f>IF($A57="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A57)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A57)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A57="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A57)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A57)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J57" s="74">
@@ -22936,7 +22936,7 @@
         <v/>
       </c>
       <c r="I58" s="76">
-        <f>IF($A58="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A58)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A58)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A58="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A58)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A58)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J58" s="74">
@@ -22998,7 +22998,7 @@
         <v/>
       </c>
       <c r="I59" s="76">
-        <f>IF($A59="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A59)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A59)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A59="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A59)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A59)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J59" s="74">
@@ -23060,7 +23060,7 @@
         <v/>
       </c>
       <c r="I60" s="76">
-        <f>IF($A60="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A60)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A60)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A60="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A60)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A60)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J60" s="74">
@@ -23122,7 +23122,7 @@
         <v/>
       </c>
       <c r="I61" s="76">
-        <f>IF($A61="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A61)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A61)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A61="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A61)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A61)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J61" s="74">
@@ -23184,7 +23184,7 @@
         <v/>
       </c>
       <c r="I62" s="76">
-        <f>IF($A62="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A62)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A62)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A62="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A62)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A62)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J62" s="74">
@@ -23246,7 +23246,7 @@
         <v/>
       </c>
       <c r="I63" s="76">
-        <f>IF($A63="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A63)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A63)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A63="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A63)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A63)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J63" s="74">
@@ -23308,7 +23308,7 @@
         <v/>
       </c>
       <c r="I64" s="76">
-        <f>IF($A64="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A64)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A64)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A64="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A64)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A64)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J64" s="74">
@@ -23370,7 +23370,7 @@
         <v/>
       </c>
       <c r="I65" s="76">
-        <f>IF($A65="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A65)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A65)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A65="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A65)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A65)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J65" s="74">
@@ -23432,7 +23432,7 @@
         <v/>
       </c>
       <c r="I66" s="76">
-        <f>IF($A66="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A66)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A66)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A66="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A66)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A66)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J66" s="74">
@@ -23494,7 +23494,7 @@
         <v/>
       </c>
       <c r="I67" s="76">
-        <f>IF($A67="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A67)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A67)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A67="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A67)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A67)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J67" s="74">
@@ -23556,7 +23556,7 @@
         <v/>
       </c>
       <c r="I68" s="76">
-        <f>IF($A68="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A68)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A68)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A68="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A68)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A68)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J68" s="74">
@@ -23618,7 +23618,7 @@
         <v/>
       </c>
       <c r="I69" s="76">
-        <f>IF($A69="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A69)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A69)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A69="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A69)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A69)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J69" s="74">
@@ -23680,7 +23680,7 @@
         <v/>
       </c>
       <c r="I70" s="76">
-        <f>IF($A70="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A70)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A70)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A70="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A70)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A70)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J70" s="74">
@@ -23742,7 +23742,7 @@
         <v/>
       </c>
       <c r="I71" s="76">
-        <f>IF($A71="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A71)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A71)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A71="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A71)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A71)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J71" s="74">
@@ -23804,7 +23804,7 @@
         <v/>
       </c>
       <c r="I72" s="76">
-        <f>IF($A72="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A72)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A72)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A72="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A72)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A72)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J72" s="74">
@@ -23866,7 +23866,7 @@
         <v/>
       </c>
       <c r="I73" s="76">
-        <f>IF($A73="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A73)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A73)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A73="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A73)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A73)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J73" s="74">
@@ -23928,7 +23928,7 @@
         <v/>
       </c>
       <c r="I74" s="76">
-        <f>IF($A74="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A74)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A74)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A74="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A74)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A74)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J74" s="74">
@@ -23990,7 +23990,7 @@
         <v/>
       </c>
       <c r="I75" s="76">
-        <f>IF($A75="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A75)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A75)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A75="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A75)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A75)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J75" s="74">
@@ -24052,7 +24052,7 @@
         <v/>
       </c>
       <c r="I76" s="76">
-        <f>IF($A76="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A76)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A76)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A76="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A76)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A76)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J76" s="74">
@@ -24114,7 +24114,7 @@
         <v/>
       </c>
       <c r="I77" s="76">
-        <f>IF($A77="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A77)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A77)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A77="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A77)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A77)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J77" s="74">
@@ -24176,7 +24176,7 @@
         <v/>
       </c>
       <c r="I78" s="76">
-        <f>IF($A78="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A78)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A78)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A78="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A78)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A78)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J78" s="74">
@@ -24238,7 +24238,7 @@
         <v/>
       </c>
       <c r="I79" s="76">
-        <f>IF($A79="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A79)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A79)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A79="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A79)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A79)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J79" s="74">
@@ -24300,7 +24300,7 @@
         <v/>
       </c>
       <c r="I80" s="76">
-        <f>IF($A80="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A80)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A80)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A80="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A80)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A80)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J80" s="74">
@@ -24362,7 +24362,7 @@
         <v/>
       </c>
       <c r="I81" s="76">
-        <f>IF($A81="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A81)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A81)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A81="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A81)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A81)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J81" s="74">
@@ -24424,7 +24424,7 @@
         <v/>
       </c>
       <c r="I82" s="76">
-        <f>IF($A82="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A82)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A82)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A82="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A82)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A82)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J82" s="74">
@@ -24486,7 +24486,7 @@
         <v/>
       </c>
       <c r="I83" s="76">
-        <f>IF($A83="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A83)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A83)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A83="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A83)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A83)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J83" s="74">
@@ -24548,7 +24548,7 @@
         <v/>
       </c>
       <c r="I84" s="76">
-        <f>IF($A84="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A84)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A84)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A84="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A84)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A84)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J84" s="74">
@@ -24610,7 +24610,7 @@
         <v/>
       </c>
       <c r="I85" s="76">
-        <f>IF($A85="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A85)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A85)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A85="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A85)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A85)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J85" s="74">
@@ -24672,7 +24672,7 @@
         <v/>
       </c>
       <c r="I86" s="76">
-        <f>IF($A86="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A86)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A86)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A86="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A86)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A86)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J86" s="74">
@@ -24734,7 +24734,7 @@
         <v/>
       </c>
       <c r="I87" s="76">
-        <f>IF($A87="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A87)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A87)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A87="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A87)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A87)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J87" s="74">
@@ -24796,7 +24796,7 @@
         <v/>
       </c>
       <c r="I88" s="76">
-        <f>IF($A88="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A88)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A88)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A88="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A88)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A88)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J88" s="74">
@@ -24858,7 +24858,7 @@
         <v/>
       </c>
       <c r="I89" s="76">
-        <f>IF($A89="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A89)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A89)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A89="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A89)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A89)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J89" s="74">
@@ -24920,7 +24920,7 @@
         <v/>
       </c>
       <c r="I90" s="76">
-        <f>IF($A90="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A90)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A90)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A90="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A90)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A90)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J90" s="74">
@@ -24982,7 +24982,7 @@
         <v/>
       </c>
       <c r="I91" s="76">
-        <f>IF($A91="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A91)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A91)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A91="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A91)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A91)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J91" s="74">
@@ -25044,7 +25044,7 @@
         <v/>
       </c>
       <c r="I92" s="76">
-        <f>IF($A92="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A92)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A92)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A92="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A92)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A92)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J92" s="74">
@@ -25106,7 +25106,7 @@
         <v/>
       </c>
       <c r="I93" s="76">
-        <f>IF($A93="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A93)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A93)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A93="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A93)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A93)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J93" s="74">
@@ -25168,7 +25168,7 @@
         <v/>
       </c>
       <c r="I94" s="76">
-        <f>IF($A94="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A94)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A94)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A94="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A94)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A94)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J94" s="74">
@@ -25230,7 +25230,7 @@
         <v/>
       </c>
       <c r="I95" s="76">
-        <f>IF($A95="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A95)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A95)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A95="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A95)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A95)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J95" s="74">
@@ -25292,7 +25292,7 @@
         <v/>
       </c>
       <c r="I96" s="76">
-        <f>IF($A96="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A96)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A96)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A96="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A96)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A96)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J96" s="74">
@@ -25354,7 +25354,7 @@
         <v/>
       </c>
       <c r="I97" s="76">
-        <f>IF($A97="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A97)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A97)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A97="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A97)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A97)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J97" s="74">
@@ -25416,7 +25416,7 @@
         <v/>
       </c>
       <c r="I98" s="76">
-        <f>IF($A98="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A98)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A98)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A98="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A98)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A98)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J98" s="74">
@@ -25478,7 +25478,7 @@
         <v/>
       </c>
       <c r="I99" s="76">
-        <f>IF($A99="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A99)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A99)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A99="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A99)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A99)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J99" s="74">
@@ -25540,7 +25540,7 @@
         <v/>
       </c>
       <c r="I100" s="76">
-        <f>IF($A100="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A100)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A100)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A100="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A100)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A100)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J100" s="74">
@@ -25602,7 +25602,7 @@
         <v/>
       </c>
       <c r="I101" s="76">
-        <f>IF($A101="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A101)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A101)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A101="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A101)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A101)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J101" s="74">
@@ -25664,7 +25664,7 @@
         <v/>
       </c>
       <c r="I102" s="76">
-        <f>IF($A102="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A102)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A102)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A102="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A102)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A102)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J102" s="74">
@@ -25726,7 +25726,7 @@
         <v/>
       </c>
       <c r="I103" s="76">
-        <f>IF($A103="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A103)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A103)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A103="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A103)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A103)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J103" s="74">
@@ -25788,7 +25788,7 @@
         <v/>
       </c>
       <c r="I104" s="76">
-        <f>IF($A104="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A104)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A104)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A104="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A104)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A104)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J104" s="74">
@@ -25850,7 +25850,7 @@
         <v/>
       </c>
       <c r="I105" s="76">
-        <f>IF($A105="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A105)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A105)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A105="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A105)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A105)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J105" s="74">
@@ -25912,7 +25912,7 @@
         <v/>
       </c>
       <c r="I106" s="76">
-        <f>IF($A106="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A106)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A106)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A106="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A106)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A106)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J106" s="74">
@@ -25974,7 +25974,7 @@
         <v/>
       </c>
       <c r="I107" s="76">
-        <f>IF($A107="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A107)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A107)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A107="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A107)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A107)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J107" s="74">
@@ -26036,7 +26036,7 @@
         <v/>
       </c>
       <c r="I108" s="76">
-        <f>IF($A108="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A108)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A108)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A108="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A108)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A108)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J108" s="74">
@@ -26098,7 +26098,7 @@
         <v/>
       </c>
       <c r="I109" s="76">
-        <f>IF($A109="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A109)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A109)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A109="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A109)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A109)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J109" s="74">
@@ -26160,7 +26160,7 @@
         <v/>
       </c>
       <c r="I110" s="76">
-        <f>IF($A110="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A110)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A110)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A110="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A110)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A110)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J110" s="74">
@@ -26222,7 +26222,7 @@
         <v/>
       </c>
       <c r="I111" s="76">
-        <f>IF($A111="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A111)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A111)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A111="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A111)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A111)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J111" s="74">
@@ -26284,7 +26284,7 @@
         <v/>
       </c>
       <c r="I112" s="76">
-        <f>IF($A112="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A112)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A112)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A112="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A112)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A112)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J112" s="74">
@@ -26346,7 +26346,7 @@
         <v/>
       </c>
       <c r="I113" s="76">
-        <f>IF($A113="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A113)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A113)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A113="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A113)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A113)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J113" s="74">
@@ -26408,7 +26408,7 @@
         <v/>
       </c>
       <c r="I114" s="76">
-        <f>IF($A114="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A114)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A114)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A114="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A114)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A114)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J114" s="74">
@@ -26470,7 +26470,7 @@
         <v/>
       </c>
       <c r="I115" s="76">
-        <f>IF($A115="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A115)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A115)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A115="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A115)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A115)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J115" s="74">
@@ -26532,7 +26532,7 @@
         <v/>
       </c>
       <c r="I116" s="76">
-        <f>IF($A116="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A116)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A116)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A116="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A116)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A116)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J116" s="74">
@@ -26594,7 +26594,7 @@
         <v/>
       </c>
       <c r="I117" s="76">
-        <f>IF($A117="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A117)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A117)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A117="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A117)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A117)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J117" s="74">
@@ -26656,7 +26656,7 @@
         <v/>
       </c>
       <c r="I118" s="76">
-        <f>IF($A118="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A118)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A118)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A118="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A118)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A118)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J118" s="74">
@@ -26718,7 +26718,7 @@
         <v/>
       </c>
       <c r="I119" s="76">
-        <f>IF($A119="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A119)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A119)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A119="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A119)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A119)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J119" s="74">
@@ -26780,7 +26780,7 @@
         <v/>
       </c>
       <c r="I120" s="76">
-        <f>IF($A120="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A120)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A120)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A120="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A120)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A120)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J120" s="74">
@@ -26842,7 +26842,7 @@
         <v/>
       </c>
       <c r="I121" s="76">
-        <f>IF($A121="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A121)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A121)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A121="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A121)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A121)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J121" s="74">
@@ -26904,7 +26904,7 @@
         <v/>
       </c>
       <c r="I122" s="76">
-        <f>IF($A122="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A122)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A122)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A122="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A122)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A122)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J122" s="74">
@@ -26966,7 +26966,7 @@
         <v/>
       </c>
       <c r="I123" s="76">
-        <f>IF($A123="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A123)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A123)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A123="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A123)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A123)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J123" s="74">
@@ -27028,7 +27028,7 @@
         <v/>
       </c>
       <c r="I124" s="76">
-        <f>IF($A124="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A124)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A124)*('10_VANZARI'!$E$5:$E$604&lt;&gt;"")*'10_VANZARI'!$A$5:$A$604))),""))</f>
+        <f>IF($A124="","",IFERROR(IF(SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A124)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))=0,"",SUMPRODUCT(MAX(('10_VANZARI'!$B$5:$B$604=$A124)*('10_VANZARI'!$E$5:$E$604&gt;0)*'10_VANZARI'!$A$5:$A$604))),""))</f>
         <v/>
       </c>
       <c r="J124" s="74">
